--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-prozent.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-prozent.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="664">
   <si>
     <t>Property</t>
   </si>
@@ -866,7 +866,7 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">pattern:code}
 </t>
   </si>
   <si>
@@ -1747,6 +1747,13 @@
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="component:&amp;lt;slice&amp;gt;.code"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>containment by OBX-4?</t>
   </si>
   <si>
@@ -1865,6 +1872,10 @@
   </si>
   <si>
     <t>Observation.component.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
   </si>
   <si>
     <t>Observation.component:predicted.code.coding:sct</t>
@@ -12829,7 +12840,7 @@
         <v>81</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>81</v>
+        <v>554</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>81</v>
@@ -12887,7 +12898,7 @@
         <v>81</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -12898,10 +12909,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13013,10 +13024,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13130,10 +13141,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13249,10 +13260,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13278,13 +13289,13 @@
         <v>232</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O93" t="s" s="2">
         <v>261</v>
@@ -13336,7 +13347,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>91</v>
@@ -13354,7 +13365,7 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>266</v>
@@ -13368,10 +13379,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13394,16 +13405,16 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>386</v>
@@ -13455,7 +13466,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13473,7 +13484,7 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>389</v>
@@ -13487,10 +13498,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13516,13 +13527,13 @@
         <v>232</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>434</v>
@@ -13574,7 +13585,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13606,10 +13617,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13635,10 +13646,10 @@
         <v>232</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>443</v>
@@ -13693,7 +13704,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13725,10 +13736,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13754,10 +13765,10 @@
         <v>82</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>494</v>
@@ -13812,7 +13823,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13844,13 +13855,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>549</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>81</v>
@@ -13875,10 +13886,10 @@
         <v>491</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>552</v>
@@ -13954,7 +13965,7 @@
         <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>81</v>
@@ -13965,10 +13976,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14080,10 +14091,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14197,10 +14208,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14316,10 +14327,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14345,13 +14356,13 @@
         <v>232</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>261</v>
@@ -14403,7 +14414,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>91</v>
@@ -14421,7 +14432,7 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>266</v>
@@ -14435,10 +14446,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14550,10 +14561,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14667,10 +14678,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14742,7 +14753,7 @@
         <v>81</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>272</v>
+        <v>594</v>
       </c>
       <c r="AC105" s="2"/>
       <c r="AD105" t="s" s="2">
@@ -14784,10 +14795,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>309</v>
@@ -14903,10 +14914,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C107" t="s" s="2">
         <v>321</v>
@@ -15022,10 +15033,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15141,10 +15152,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15167,16 +15178,16 @@
         <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O109" t="s" s="2">
         <v>386</v>
@@ -15216,7 +15227,7 @@
         <v>81</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AC109" s="2"/>
       <c r="AD109" t="s" s="2">
@@ -15226,7 +15237,7 @@
         <v>117</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15244,7 +15255,7 @@
         <v>81</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>389</v>
@@ -15258,13 +15269,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>81</v>
@@ -15289,13 +15300,13 @@
         <v>382</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O110" t="s" s="2">
         <v>386</v>
@@ -15347,7 +15358,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15365,7 +15376,7 @@
         <v>81</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>389</v>
@@ -15379,10 +15390,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15494,10 +15505,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15611,10 +15622,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15730,10 +15741,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15849,10 +15860,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15966,10 +15977,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16083,10 +16094,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16202,10 +16213,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16231,13 +16242,13 @@
         <v>232</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O118" t="s" s="2">
         <v>434</v>
@@ -16289,7 +16300,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16321,10 +16332,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16350,10 +16361,10 @@
         <v>232</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>443</v>
@@ -16408,7 +16419,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16440,10 +16451,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16469,10 +16480,10 @@
         <v>82</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>494</v>
@@ -16527,7 +16538,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16559,13 +16570,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>549</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>81</v>
@@ -16590,10 +16601,10 @@
         <v>491</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>552</v>
@@ -16669,7 +16680,7 @@
         <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
@@ -16680,10 +16691,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16795,10 +16806,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16912,10 +16923,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17031,10 +17042,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17060,13 +17071,13 @@
         <v>232</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O125" t="s" s="2">
         <v>261</v>
@@ -17118,7 +17129,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>91</v>
@@ -17136,7 +17147,7 @@
         <v>81</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>266</v>
@@ -17150,10 +17161,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17265,10 +17276,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17382,10 +17393,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17457,7 +17468,7 @@
         <v>81</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>272</v>
+        <v>594</v>
       </c>
       <c r="AC128" s="2"/>
       <c r="AD128" t="s" s="2">
@@ -17499,10 +17510,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C129" t="s" s="2">
         <v>309</v>
@@ -17618,10 +17629,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C130" t="s" s="2">
         <v>321</v>
@@ -17737,10 +17748,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17856,10 +17867,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17882,16 +17893,16 @@
         <v>92</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O132" t="s" s="2">
         <v>386</v>
@@ -17931,7 +17942,7 @@
         <v>81</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AC132" s="2"/>
       <c r="AD132" t="s" s="2">
@@ -17941,7 +17952,7 @@
         <v>117</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17959,7 +17970,7 @@
         <v>81</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>389</v>
@@ -17973,13 +17984,13 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D133" t="s" s="2">
         <v>81</v>
@@ -18004,13 +18015,13 @@
         <v>382</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O133" t="s" s="2">
         <v>386</v>
@@ -18062,7 +18073,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18080,7 +18091,7 @@
         <v>81</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>389</v>
@@ -18094,10 +18105,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18209,10 +18220,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18326,10 +18337,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18445,10 +18456,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18564,10 +18575,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18681,10 +18692,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18798,10 +18809,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18917,10 +18928,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18946,13 +18957,13 @@
         <v>232</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O141" t="s" s="2">
         <v>434</v>
@@ -19004,7 +19015,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19036,10 +19047,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19065,10 +19076,10 @@
         <v>232</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>443</v>
@@ -19123,7 +19134,7 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19155,10 +19166,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19184,10 +19195,10 @@
         <v>82</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N143" t="s" s="2">
         <v>494</v>
@@ -19242,7 +19253,7 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19274,13 +19285,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>549</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>81</v>
@@ -19305,10 +19316,10 @@
         <v>491</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>552</v>
@@ -19384,7 +19395,7 @@
         <v>81</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>81</v>
@@ -19395,10 +19406,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19510,10 +19521,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19627,10 +19638,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19746,10 +19757,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19775,13 +19786,13 @@
         <v>232</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O148" t="s" s="2">
         <v>261</v>
@@ -19833,7 +19844,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>91</v>
@@ -19851,7 +19862,7 @@
         <v>81</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>266</v>
@@ -19865,10 +19876,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19980,10 +19991,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20097,10 +20108,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20172,7 +20183,7 @@
         <v>81</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>272</v>
+        <v>594</v>
       </c>
       <c r="AC151" s="2"/>
       <c r="AD151" t="s" s="2">
@@ -20214,10 +20225,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C152" t="s" s="2">
         <v>309</v>
@@ -20264,7 +20275,7 @@
         <v>81</v>
       </c>
       <c r="S152" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="T152" t="s" s="2">
         <v>81</v>
@@ -20333,10 +20344,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20452,10 +20463,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20478,16 +20489,16 @@
         <v>92</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O154" t="s" s="2">
         <v>386</v>
@@ -20539,7 +20550,7 @@
         <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -20557,7 +20568,7 @@
         <v>81</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>389</v>
@@ -20571,10 +20582,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20600,13 +20611,13 @@
         <v>232</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O155" t="s" s="2">
         <v>434</v>
@@ -20658,7 +20669,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -20690,10 +20701,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20719,10 +20730,10 @@
         <v>232</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N156" t="s" s="2">
         <v>443</v>
@@ -20777,7 +20788,7 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -20809,10 +20820,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20838,10 +20849,10 @@
         <v>82</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N157" t="s" s="2">
         <v>494</v>
@@ -20896,7 +20907,7 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
